--- a/e2e/downloadedFile/sub_Master_Prorate.xlsx
+++ b/e2e/downloadedFile/sub_Master_Prorate.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="36">
   <si>
     <t>DAFTAR PERHITUNGAN GAJI PRORATA KARYAWAN</t>
   </si>
@@ -68,13 +68,10 @@
     <t>GAJI PRORATA 2</t>
   </si>
   <si>
-    <t>0000002</t>
-  </si>
-  <si>
-    <t>Syifa Hadju</t>
-  </si>
-  <si>
-    <t>Accounting Support Officer</t>
+    <t>RIMBUN SIBURIAN</t>
+  </si>
+  <si>
+    <t>Quality Assuance Senior Engineer</t>
   </si>
   <si>
     <t>7-Jan-26</t>
@@ -86,10 +83,10 @@
     <t>14-Jan-26</t>
   </si>
   <si>
-    <t>$ 11.77</t>
-  </si>
-  <si>
-    <t>$ -11.77</t>
+    <t>$ 103.23</t>
+  </si>
+  <si>
+    <t>$ -103.23</t>
   </si>
   <si>
     <t>15-Jan-26</t>
@@ -98,16 +95,16 @@
     <t>31-Jan-26</t>
   </si>
   <si>
-    <t>$ 31.26</t>
-  </si>
-  <si>
-    <t>$ 43.03</t>
+    <t>$ 274.19</t>
+  </si>
+  <si>
+    <t>$ 377.42</t>
   </si>
   <si>
     <t>TOTAL</t>
   </si>
   <si>
-    <t>DILI, 14 AGUSTUS 2026</t>
+    <t>DILI, 18 AGUSTUS 2026</t>
   </si>
   <si>
     <t>Human Resource</t>
@@ -541,9 +538,9 @@
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="true" style="0"/>
-    <col min="2" max="2" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="13.997" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="31.707" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="6.998" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="18.71" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="38.848" bestFit="true" customWidth="true" style="0"/>
     <col min="5" max="5" width="11.711" bestFit="true" customWidth="true" style="0"/>
     <col min="6" max="6" width="12.854" bestFit="true" customWidth="true" style="0"/>
     <col min="7" max="7" width="13.997" bestFit="true" customWidth="true" style="0"/>
@@ -652,58 +649,58 @@
       <c r="A6" s="3">
         <v>1</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="3">
+        <v>81010</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3">
+        <v>30</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="G6" s="3">
-        <v>31</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="J6" s="3">
         <v>8</v>
       </c>
       <c r="K6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="L6" s="3" t="s">
+      <c r="M6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M6" s="3" t="s">
+      <c r="N6" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="O6" s="3">
         <v>17</v>
       </c>
       <c r="P6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q6" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="Q6" s="3" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -721,7 +718,7 @@
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
       <c r="Q7" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -729,18 +726,18 @@
     </row>
     <row r="9" spans="1:17">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E9"/>
       <c r="I9"/>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E10"/>
       <c r="G10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:17" customHeight="1" ht="37.5">
@@ -750,20 +747,20 @@
     </row>
     <row r="12" spans="1:17">
       <c r="A12" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E12"/>
       <c r="G12" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:17">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E13"/>
       <c r="G13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
